--- a/中学生26秋教学服务看板-访问链接.xlsx
+++ b/中学生26秋教学服务看板-访问链接.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="看板访问链接" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,18 +26,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <color rgb="002563EB"/>
+      <sz val="11"/>
       <u val="single"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="002563EB"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,8 +64,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
@@ -76,11 +86,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,746 +458,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>版本类型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>访问链接</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>汇总版</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>中学生26秋教学服务看板-汇总版本</t>
-        </is>
-      </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/中学生26秋教学服务看板-汇总版本.html</t>
+          <t>汇总版本</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>中学七宝宝龙分校</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学七宝宝龙分校.html</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>中学三林分校</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学三林分校.html</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>中学九亭贝尚坊分校</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学九亭贝尚坊分校.html</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>中学五角场分校</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学五角场分校.html</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>中学人民广场分校</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学人民广场分校.html</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>中学八佰伴分校</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学八佰伴分校.html</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>中学共江分校</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学共江分校.html</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>中学南方分校</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学南方分校.html</t>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>中学南桥分校</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学南桥分校.html</t>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>中学南翔分校</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学南翔分校.html</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>中学唐镇分校</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学唐镇分校.html</t>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>中学大华分校</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学大华分校.html</t>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>中学天山分校</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学天山分校.html</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>中学学科部</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学学科部.html</t>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>中学安亭财富广场分校</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学安亭财富广场分校.html</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>中学徐汇分校</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学徐汇分校.html</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>中学打浦桥日月光分校</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学打浦桥日月光分校.html</t>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>中学控江分校</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学控江分校.html</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>中学曹杨我格分校</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学曹杨我格分校.html</t>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>中学松江分校</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学松江分校.html</t>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>中学梅川路分校</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学梅川路分校.html</t>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>中学歌林春天分校</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学歌林春天分校.html</t>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>中学浦东川沙分校</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学浦东川沙分校.html</t>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>中学浦江生活广场分校</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学浦江生活广场分校.html</t>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>中学牡丹江分校</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学牡丹江分校.html</t>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>中学瑞虹分校</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学瑞虹分校.html</t>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>中学生金桥分校</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学生金桥分校.html</t>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>中学田林分校</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学田林分校.html</t>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>中学锦绣分校</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学锦绣分校.html</t>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>中学长宁来福士分校</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学长宁来福士分校.html</t>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>中学长桥分校</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学长桥分校.html</t>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>中学顾村分校</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学顾村分校.html</t>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>中学颛桥分校</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学颛桥分校.html</t>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>校区版</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>校区版</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>中学高境分校</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>https://wco120178.github.io/zxs-26autumn-dashboard/campus/中学生26秋教学服务看板-中学高境分校.html</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>点击访问</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>中学生26秋教学服务看板 - 公网访问链接</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【汇总版】包含全平台数据：区域排行、校区排行、班主任排行、教师排行、学员列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【校区版】仅包含该校区数据：班主任排行、教师排行、学员列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>链接特性：</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 支持公网访问，可转发分享</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 链接固定不变，后续数据/样式更新后链接保持一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 点击链接直接在浏览器打开，无需登录</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>数据更新日期：2026-10-22</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>